--- a/order_forms/048_princess_photo_shoot--order_forms.xlsx
+++ b/order_forms/048_princess_photo_shoot--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>princess_photo_shoot_form</t>
+          <t>Princess Photo Shoot Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>photo_session_details</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Photo Session Details</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,40 +607,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>booking_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Booking Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>booking_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>Booking Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>photo_session_details</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>photo_session_details</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,63 +676,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>booking_date</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>booking_date</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>booking_time</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>booking_time</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>User ID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>User Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_title</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>form_description</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>Form Description</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>form_category</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>Form Category</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_ids</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>Form IDs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -934,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>user_phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>User Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -957,64 +957,64 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>photo_session_details_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Photo Session Details 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>photo_session_booking_date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>Photo Session Booking Date</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>user_phone</t>
+          <t>photo_session_booking_time</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>user_phone</t>
+          <t>Photo Session Booking Time</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1026,64 +1026,317 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>photo_session_details</t>
+          <t>user_phone2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>photo_session_details</t>
+          <t>User Phone2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>photo_session_booking_date</t>
+          <t>photo_session_booking</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>photo_session_booking_date</t>
+          <t>Photo Session Booking</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>photo_session_booking_time</t>
+          <t>photo_session_booking_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>photo_session_booking_time</t>
+          <t>Photo Session Booking 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>photo_session_booking_time_2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Photo Session Booking Time 2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>photo_session_booking_date_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Photo Session Booking Date 2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>form_id2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Form Id2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>form_id2_2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Form Id2 2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>user_phone_2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>User Phone 2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>photo_session_booking_date2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Photo Session Booking Date2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>photo_session_booking_time2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Photo Session Booking Time2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>assigned_tool2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Assigned Tool2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>assigned_tool2_2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Assigned Tool2 2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>photo_session_details2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Photo Session Details2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>photo_session_details2_2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Photo Session Details2 2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
